--- a/Asignacion 1/Datos Deuterio.xlsx
+++ b/Asignacion 1/Datos Deuterio.xlsx
@@ -1,36 +1,65 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29823"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f5f906da8c23dd95/Desktop/Icesi_Pregrado/2026-1/termo 2/Asignacion 1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="84" documentId="11_F25DC773A252ABDACC10485489D862385BDE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1670C57C-F4A2-4AD9-B7EF-9FE9B0EE89F7}"/>
+  <xr:revisionPtr revIDLastSave="110" documentId="11_F25DC773A252ABDACC10485489D862385BDE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{99439243-D526-4161-8D69-EFB307C6F97B}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="1848" yWindow="1848" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>T</t>
   </si>
   <si>
     <t>B</t>
+  </si>
+  <si>
+    <t>1/T</t>
+  </si>
+  <si>
+    <t>a_vir</t>
+  </si>
+  <si>
+    <t>b_vir</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>B_2</t>
   </si>
 </sst>
 </file>
@@ -557,7 +586,583 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>B_2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.21132786526684164"/>
+                  <c:y val="8.8815981335666379E-3"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$E$2:$E$30</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="29"/>
+                <c:pt idx="0">
+                  <c:v>1.1904761904761904E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.1363636363636364E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.0869565217391304E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.0416666666666666E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.0909090909090905E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8.6956521739130436E-3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8.3333333333333332E-3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>7.6923076923076927E-3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>7.1428571428571426E-3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>6.6666666666666671E-3</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>6.2500000000000003E-3</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>5.8823529411764705E-3</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>5.5555555555555558E-3</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5.263157894736842E-3</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>4.5454545454545452E-3</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>4.1666666666666666E-3</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3.8461538461538464E-3</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>3.6609921288669233E-3</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>3.5714285714285713E-3</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>3.3333333333333335E-3</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>3.1250000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2.9411764705882353E-3</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2.7777777777777779E-3</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2.6798874447273215E-3</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2.631578947368421E-3</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2.3809523809523812E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$F$2:$F$30</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="29"/>
+                <c:pt idx="0">
+                  <c:v>-10.4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-8.6999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-7</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-4.2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-1.3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4.5999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>7.1</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>8.1</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>8.9</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>9.5</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>10.199999999999999</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>11.3</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>12.2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>12.8</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>13.1</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>13.2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>13.5</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>14.4</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>14.7</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>14.9</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>15.2</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>15.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-AC0C-4048-90F4-F1035BA3CABC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="816216847"/>
+        <c:axId val="816217327"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="816216847"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="816217327"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="816217327"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="816216847"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -1113,20 +1718,536 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>34018</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>16328</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>319767</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>84364</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>421821</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>136072</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>95249</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>27214</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1146,6 +2267,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>118241</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>117366</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>398517</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E380FE09-9701-E94D-2C7A-A3526BBD11C1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1417,246 +2574,483 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:W30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
+      <c r="E1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>84</v>
       </c>
       <c r="B2">
         <v>-10.4</v>
       </c>
+      <c r="E2">
+        <f>1/A2</f>
+        <v>1.1904761904761904E-2</v>
+      </c>
+      <c r="F2">
+        <v>-10.4</v>
+      </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>88</v>
       </c>
       <c r="B3">
         <v>-8.6999999999999993</v>
       </c>
+      <c r="E3">
+        <f>1/A3</f>
+        <v>1.1363636363636364E-2</v>
+      </c>
+      <c r="F3">
+        <v>-8.6999999999999993</v>
+      </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>92</v>
       </c>
       <c r="B4">
         <v>-7</v>
       </c>
+      <c r="E4">
+        <f>1/A4</f>
+        <v>1.0869565217391304E-2</v>
+      </c>
+      <c r="F4">
+        <v>-7</v>
+      </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>96</v>
       </c>
       <c r="B5">
         <v>-5</v>
       </c>
+      <c r="E5">
+        <f>1/A5</f>
+        <v>1.0416666666666666E-2</v>
+      </c>
+      <c r="F5">
+        <v>-5</v>
+      </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>100</v>
       </c>
       <c r="B6">
         <v>-4.2</v>
       </c>
+      <c r="E6">
+        <f>1/A6</f>
+        <v>0.01</v>
+      </c>
+      <c r="F6">
+        <v>-4.2</v>
+      </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>110</v>
       </c>
       <c r="B7">
         <v>-1.3</v>
       </c>
+      <c r="E7">
+        <f>1/A7</f>
+        <v>9.0909090909090905E-3</v>
+      </c>
+      <c r="F7">
+        <v>-1.3</v>
+      </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>115</v>
       </c>
       <c r="B8">
         <v>0</v>
       </c>
+      <c r="E8">
+        <f>1/A8</f>
+        <v>8.6956521739130436E-3</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>120</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
+      <c r="E9">
+        <f>1/A9</f>
+        <v>8.3333333333333332E-3</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>130</v>
       </c>
       <c r="B10">
         <v>3</v>
       </c>
+      <c r="E10">
+        <f>1/A10</f>
+        <v>7.6923076923076927E-3</v>
+      </c>
+      <c r="F10">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>140</v>
       </c>
       <c r="B11">
         <v>4.5999999999999996</v>
       </c>
+      <c r="E11">
+        <f>1/A11</f>
+        <v>7.1428571428571426E-3</v>
+      </c>
+      <c r="F11">
+        <v>4.5999999999999996</v>
+      </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>150</v>
       </c>
       <c r="B12">
         <v>6</v>
       </c>
+      <c r="E12">
+        <f>1/A12</f>
+        <v>6.6666666666666671E-3</v>
+      </c>
+      <c r="F12">
+        <v>6</v>
+      </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>160</v>
       </c>
       <c r="B13">
         <v>7.1</v>
       </c>
+      <c r="E13">
+        <f>1/A13</f>
+        <v>6.2500000000000003E-3</v>
+      </c>
+      <c r="F13">
+        <v>7.1</v>
+      </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>170</v>
       </c>
       <c r="B14">
         <v>8.1</v>
       </c>
+      <c r="E14">
+        <f>1/A14</f>
+        <v>5.8823529411764705E-3</v>
+      </c>
+      <c r="F14">
+        <v>8.1</v>
+      </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>180</v>
       </c>
       <c r="B15">
         <v>8.9</v>
       </c>
+      <c r="E15">
+        <f>1/A15</f>
+        <v>5.5555555555555558E-3</v>
+      </c>
+      <c r="F15">
+        <v>8.9</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>5</v>
+      </c>
+      <c r="R15">
+        <f>-2669.8*8.3145*-1</f>
+        <v>22198.052100000004</v>
+      </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>190</v>
       </c>
       <c r="B16">
         <v>9.5</v>
       </c>
+      <c r="E16">
+        <f>1/A16</f>
+        <v>5.263157894736842E-3</v>
+      </c>
+      <c r="F16">
+        <v>9.5</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>6</v>
+      </c>
+      <c r="R16">
+        <f>22.813</f>
+        <v>22.812999999999999</v>
+      </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>200</v>
       </c>
       <c r="B17">
         <v>10.199999999999999</v>
       </c>
+      <c r="E17">
+        <f>1/A17</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="F17">
+        <v>10.199999999999999</v>
+      </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>220</v>
       </c>
       <c r="B18">
         <v>11.3</v>
       </c>
+      <c r="E18">
+        <f>1/A18</f>
+        <v>4.5454545454545452E-3</v>
+      </c>
+      <c r="F18">
+        <v>11.3</v>
+      </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>240</v>
       </c>
       <c r="B19">
         <v>12.2</v>
       </c>
+      <c r="E19">
+        <f>1/A19</f>
+        <v>4.1666666666666666E-3</v>
+      </c>
+      <c r="F19">
+        <v>12.2</v>
+      </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>260</v>
       </c>
       <c r="B20">
         <v>12.8</v>
       </c>
+      <c r="E20">
+        <f>1/A20</f>
+        <v>3.8461538461538464E-3</v>
+      </c>
+      <c r="F20">
+        <v>12.8</v>
+      </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>273.14999999999998</v>
       </c>
       <c r="B21">
         <v>13.1</v>
       </c>
+      <c r="E21">
+        <f>1/A21</f>
+        <v>3.6609921288669233E-3</v>
+      </c>
+      <c r="F21">
+        <v>13.1</v>
+      </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>280</v>
       </c>
       <c r="B22">
         <v>13.2</v>
       </c>
+      <c r="E22">
+        <f>1/A22</f>
+        <v>3.5714285714285713E-3</v>
+      </c>
+      <c r="F22">
+        <v>13.2</v>
+      </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>300</v>
       </c>
       <c r="B23">
         <v>13.5</v>
       </c>
+      <c r="E23">
+        <f>1/A23</f>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="F23">
+        <v>13.5</v>
+      </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>320</v>
       </c>
       <c r="B24">
         <v>14</v>
       </c>
+      <c r="E24">
+        <f>1/A24</f>
+        <v>3.1250000000000002E-3</v>
+      </c>
+      <c r="F24">
+        <v>14</v>
+      </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>340</v>
       </c>
       <c r="B25">
         <v>14.4</v>
       </c>
+      <c r="E25">
+        <f>1/A25</f>
+        <v>2.9411764705882353E-3</v>
+      </c>
+      <c r="F25">
+        <v>14.4</v>
+      </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>360</v>
       </c>
       <c r="B26">
         <v>14.7</v>
       </c>
+      <c r="E26">
+        <f>1/A26</f>
+        <v>2.7777777777777779E-3</v>
+      </c>
+      <c r="F26">
+        <v>14.7</v>
+      </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>373.15</v>
       </c>
       <c r="B27">
         <v>14.9</v>
       </c>
+      <c r="E27">
+        <f>1/A27</f>
+        <v>2.6798874447273215E-3</v>
+      </c>
+      <c r="F27">
+        <v>14.9</v>
+      </c>
+      <c r="V27" t="s">
+        <v>3</v>
+      </c>
+      <c r="W27">
+        <f>-0.0004*8.3145*-1</f>
+        <v>3.3258000000000003E-3</v>
+      </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>380</v>
       </c>
       <c r="B28">
         <v>15</v>
       </c>
+      <c r="E28">
+        <f>1/A28</f>
+        <v>2.631578947368421E-3</v>
+      </c>
+      <c r="F28">
+        <v>15</v>
+      </c>
+      <c r="V28" t="s">
+        <v>4</v>
+      </c>
+      <c r="W28">
+        <f>0.0085</f>
+        <v>8.5000000000000006E-3</v>
+      </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>400</v>
       </c>
       <c r="B29">
         <v>15.2</v>
       </c>
+      <c r="E29">
+        <f>1/A29</f>
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="F29">
+        <v>15.2</v>
+      </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>420</v>
       </c>
       <c r="B30">
+        <v>15.5</v>
+      </c>
+      <c r="E30">
+        <f>1/A30</f>
+        <v>2.3809523809523812E-3</v>
+      </c>
+      <c r="F30">
         <v>15.5</v>
       </c>
     </row>
